--- a/artfynd/A 7806-2024 artfynd.xlsx
+++ b/artfynd/A 7806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118804813</v>
+        <v>119142903</v>
       </c>
       <c r="B2" t="n">
-        <v>90567</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3277</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höktjärnbodarna (Höktjärnbodarna), Jmt</t>
+          <t>Höktjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457368</v>
+        <v>457299</v>
       </c>
       <c r="R2" t="n">
-        <v>7075574</v>
+        <v>7075621</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119142876</v>
+        <v>119142815</v>
       </c>
       <c r="B3" t="n">
-        <v>90556</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457422</v>
+        <v>457630</v>
       </c>
       <c r="R3" t="n">
-        <v>7075440</v>
+        <v>7074693</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119142774</v>
+        <v>119142888</v>
       </c>
       <c r="B4" t="n">
-        <v>91252</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457618</v>
+        <v>457458</v>
       </c>
       <c r="R4" t="n">
-        <v>7074693</v>
+        <v>7075535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119142937</v>
+        <v>119142863</v>
       </c>
       <c r="B5" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457410</v>
+        <v>457403</v>
       </c>
       <c r="R5" t="n">
-        <v>7074673</v>
+        <v>7075406</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,6 +1059,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1095,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119142884</v>
+        <v>119142850</v>
       </c>
       <c r="B6" t="n">
-        <v>79606</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457273</v>
+        <v>457278</v>
       </c>
       <c r="R6" t="n">
-        <v>7075619</v>
+        <v>7075621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,37 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119142911</v>
+        <v>119142876</v>
       </c>
       <c r="B7" t="n">
-        <v>90525</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457354</v>
+        <v>457422</v>
       </c>
       <c r="R7" t="n">
-        <v>7074767</v>
+        <v>7075440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,15 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119142927</v>
+        <v>119142937</v>
       </c>
       <c r="B8" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457351</v>
+        <v>457410</v>
       </c>
       <c r="R8" t="n">
-        <v>7074751</v>
+        <v>7074673</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,37 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119142902</v>
+        <v>119142752</v>
       </c>
       <c r="B9" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457307</v>
+        <v>457610</v>
       </c>
       <c r="R9" t="n">
-        <v>7075613</v>
+        <v>7074713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,11 +1473,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1529,50 +1493,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119142922</v>
+        <v>119202142</v>
       </c>
       <c r="B10" t="n">
-        <v>93914</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2359</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Taggstjärnmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mnium spinosum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Voit) Schwägr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Höktjärnrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457278</v>
+        <v>458079</v>
       </c>
       <c r="R10" t="n">
-        <v>7075615</v>
+        <v>7074412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,31 +1578,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>119142755</v>
       </c>
       <c r="B11" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,15 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119142860</v>
+        <v>89603636</v>
       </c>
       <c r="B12" t="n">
-        <v>80559</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,34 +1702,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229558</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Höktjärnrun, Jmt</t>
+          <t>Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457287</v>
+        <v>456373</v>
       </c>
       <c r="R12" t="n">
-        <v>7075658</v>
+        <v>7076674</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,17 +1751,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Föllinge</t>
+          <t>Hotagen</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,40 +1772,30 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119142942</v>
+        <v>119142938</v>
       </c>
       <c r="B13" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1803,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457237</v>
+        <v>457277</v>
       </c>
       <c r="R13" t="n">
-        <v>7075754</v>
+        <v>7075632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,6 +1873,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>död ved sälg</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1958,15 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119142895</v>
+        <v>119142884</v>
       </c>
       <c r="B14" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,21 +1909,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457203</v>
+        <v>457273</v>
       </c>
       <c r="R14" t="n">
-        <v>7075725</v>
+        <v>7075619</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,6 +1979,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2064,37 +2004,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119142805</v>
+        <v>119142890</v>
       </c>
       <c r="B15" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457880</v>
+        <v>457304</v>
       </c>
       <c r="R15" t="n">
-        <v>7074714</v>
+        <v>7075614</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2088,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2175,37 +2110,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119142944</v>
+        <v>119142909</v>
       </c>
       <c r="B16" t="n">
-        <v>98239</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2215,10 +2145,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457328</v>
+        <v>457289</v>
       </c>
       <c r="R16" t="n">
-        <v>7074859</v>
+        <v>7075653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,6 +2191,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2284,12 +2219,7 @@
         <v>119142933</v>
       </c>
       <c r="B17" t="n">
-        <v>79606</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,37 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119142868</v>
+        <v>119142935</v>
       </c>
       <c r="B18" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457330</v>
+        <v>457336</v>
       </c>
       <c r="R18" t="n">
-        <v>7074858</v>
+        <v>7074860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,37 +2428,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119142934</v>
+        <v>119142922</v>
       </c>
       <c r="B19" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95943</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2359</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Taggstjärnmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Mnium spinosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Voit) Schwägr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457282</v>
+        <v>457278</v>
       </c>
       <c r="R19" t="n">
-        <v>7075638</v>
+        <v>7075615</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,11 +2509,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2614,50 +2529,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119142837</v>
+        <v>119202240</v>
       </c>
       <c r="B20" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95943</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2359</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Taggstjärnmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Mnium spinosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Voit) Schwägr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Höktjärnrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457273</v>
+        <v>458100</v>
       </c>
       <c r="R20" t="n">
-        <v>7075635</v>
+        <v>7074550</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,61 +2611,47 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119142954</v>
+        <v>119142829</v>
       </c>
       <c r="B21" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457215</v>
+        <v>457437</v>
       </c>
       <c r="R21" t="n">
-        <v>7075722</v>
+        <v>7075627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,11 +2707,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2836,37 +2727,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119142909</v>
+        <v>119142786</v>
       </c>
       <c r="B22" t="n">
-        <v>79606</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>2697</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig tuffmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Palustriella decipiens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(De Not.) Ochyra</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457289</v>
+        <v>457189</v>
       </c>
       <c r="R22" t="n">
-        <v>7075653</v>
+        <v>7074778</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,11 +2808,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2947,15 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119142776</v>
+        <v>119142926</v>
       </c>
       <c r="B23" t="n">
-        <v>90525</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,21 +2839,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>2697</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordlig tuffmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Palustriella decipiens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(De Not.) Ochyra</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457894</v>
+        <v>457444</v>
       </c>
       <c r="R23" t="n">
-        <v>7074702</v>
+        <v>7075599</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3053,15 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119142852</v>
+        <v>119142806</v>
       </c>
       <c r="B24" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96155</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>2699</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Klotuffmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Palustriella falcata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Hedenäs</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3093,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457238</v>
+        <v>457461</v>
       </c>
       <c r="R24" t="n">
-        <v>7075699</v>
+        <v>7075045</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,11 +3010,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3164,15 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119142831</v>
+        <v>119202224</v>
       </c>
       <c r="B25" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3180,34 +3041,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höktjärnrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457256</v>
+        <v>458090</v>
       </c>
       <c r="R25" t="n">
-        <v>7075626</v>
+        <v>7074520</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,79 +3112,60 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119142791</v>
+        <v>119202207</v>
       </c>
       <c r="B26" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Höktjärnrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457579</v>
+        <v>458125</v>
       </c>
       <c r="R26" t="n">
-        <v>7074705</v>
+        <v>7074436</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,69 +3212,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119142877</v>
+        <v>118804813</v>
       </c>
       <c r="B27" t="n">
-        <v>96860</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>3277</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höktjärnrun, Jmt</t>
+          <t>Höktjärnbodarna, Höktjärnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457202</v>
+        <v>457368</v>
       </c>
       <c r="R27" t="n">
-        <v>7075739</v>
+        <v>7075574</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3456,12 +3289,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,53 +3309,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119142861</v>
+        <v>119142774</v>
       </c>
       <c r="B28" t="n">
-        <v>41110</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>215713</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3532,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457383</v>
+        <v>457618</v>
       </c>
       <c r="R28" t="n">
-        <v>7074720</v>
+        <v>7074693</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,15 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119142832</v>
+        <v>119142776</v>
       </c>
       <c r="B29" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3638,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457335</v>
+        <v>457894</v>
       </c>
       <c r="R29" t="n">
-        <v>7074861</v>
+        <v>7074702</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,11 +3503,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>gammal sälg</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3709,37 +3523,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119142817</v>
+        <v>119142911</v>
       </c>
       <c r="B30" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3749,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457580</v>
+        <v>457354</v>
       </c>
       <c r="R30" t="n">
-        <v>7074699</v>
+        <v>7074767</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3815,37 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119142862</v>
+        <v>119142948</v>
       </c>
       <c r="B31" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3855,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457491</v>
+        <v>457426</v>
       </c>
       <c r="R31" t="n">
-        <v>7075393</v>
+        <v>7074667</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3901,11 +3705,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3929,16 +3728,11 @@
         <v>119142758</v>
       </c>
       <c r="B32" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4032,50 +3826,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119142890</v>
+        <v>119202247</v>
       </c>
       <c r="B33" t="n">
-        <v>79606</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Höktjärnrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457304</v>
+        <v>458079</v>
       </c>
       <c r="R33" t="n">
-        <v>7075614</v>
+        <v>7074414</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,39 +3908,25 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119142888</v>
+        <v>119142771</v>
       </c>
       <c r="B34" t="n">
-        <v>86876</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,21 +3934,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4183,10 +3958,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457458</v>
+        <v>457895</v>
       </c>
       <c r="R34" t="n">
-        <v>7075535</v>
+        <v>7074715</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,15 +4024,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119142752</v>
+        <v>119142780</v>
       </c>
       <c r="B35" t="n">
-        <v>90574</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4265,21 +4035,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4289,10 +4059,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457610</v>
+        <v>457219</v>
       </c>
       <c r="R35" t="n">
-        <v>7074713</v>
+        <v>7074747</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,37 +4125,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119142870</v>
+        <v>119142792</v>
       </c>
       <c r="B36" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4395,10 +4160,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457301</v>
+        <v>457807</v>
       </c>
       <c r="R36" t="n">
-        <v>7075616</v>
+        <v>7074681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,11 +4206,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4466,37 +4226,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119142873</v>
+        <v>119142817</v>
       </c>
       <c r="B37" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4506,10 +4261,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457187</v>
+        <v>457580</v>
       </c>
       <c r="R37" t="n">
-        <v>7075735</v>
+        <v>7074699</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4552,11 +4307,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4577,37 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119142923</v>
+        <v>119142895</v>
       </c>
       <c r="B38" t="n">
-        <v>96860</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4617,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457271</v>
+        <v>457203</v>
       </c>
       <c r="R38" t="n">
-        <v>7075696</v>
+        <v>7075725</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4683,15 +4428,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119142903</v>
+        <v>119142927</v>
       </c>
       <c r="B39" t="n">
-        <v>74631</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,21 +4439,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4723,10 +4463,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457299</v>
+        <v>457351</v>
       </c>
       <c r="R39" t="n">
-        <v>7075621</v>
+        <v>7074751</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,15 +4529,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119142938</v>
+        <v>119142942</v>
       </c>
       <c r="B40" t="n">
-        <v>74641</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,21 +4540,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4829,10 +4564,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457277</v>
+        <v>457237</v>
       </c>
       <c r="R40" t="n">
-        <v>7075632</v>
+        <v>7075754</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4875,11 +4610,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>död ved sälg</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4900,37 +4630,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119142824</v>
+        <v>119142837</v>
       </c>
       <c r="B41" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4940,10 +4665,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457186</v>
+        <v>457273</v>
       </c>
       <c r="R41" t="n">
-        <v>7075734</v>
+        <v>7075635</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5011,15 +4736,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119142815</v>
+        <v>119142862</v>
       </c>
       <c r="B42" t="n">
-        <v>86876</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,21 +4747,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5051,10 +4771,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457630</v>
+        <v>457491</v>
       </c>
       <c r="R42" t="n">
-        <v>7074693</v>
+        <v>7075393</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5097,6 +4817,11 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5117,15 +4842,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119142835</v>
+        <v>119142902</v>
       </c>
       <c r="B43" t="n">
-        <v>90578</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5133,21 +4853,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5157,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457268</v>
+        <v>457307</v>
       </c>
       <c r="R43" t="n">
-        <v>7075700</v>
+        <v>7075613</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5203,6 +4923,11 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5223,15 +4948,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119142771</v>
+        <v>119142934</v>
       </c>
       <c r="B44" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5239,21 +4959,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5263,10 +4983,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457895</v>
+        <v>457282</v>
       </c>
       <c r="R44" t="n">
-        <v>7074715</v>
+        <v>7075638</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5309,6 +5029,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5329,37 +5054,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119142950</v>
+        <v>119142954</v>
       </c>
       <c r="B45" t="n">
-        <v>79633</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5089,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457264</v>
+        <v>457215</v>
       </c>
       <c r="R45" t="n">
-        <v>7075702</v>
+        <v>7075722</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5415,6 +5135,11 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5435,37 +5160,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119142863</v>
+        <v>119142950</v>
       </c>
       <c r="B46" t="n">
-        <v>91126</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>6461</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5475,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457403</v>
+        <v>457264</v>
       </c>
       <c r="R46" t="n">
-        <v>7075406</v>
+        <v>7075702</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5521,11 +5241,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5546,37 +5261,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119142850</v>
+        <v>119142805</v>
       </c>
       <c r="B47" t="n">
-        <v>78606</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5586,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457278</v>
+        <v>457880</v>
       </c>
       <c r="R47" t="n">
-        <v>7075621</v>
+        <v>7074714</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,7 +5345,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5657,15 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119142859</v>
+        <v>119142831</v>
       </c>
       <c r="B48" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,21 +5378,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5697,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457336</v>
+        <v>457256</v>
       </c>
       <c r="R48" t="n">
-        <v>7074855</v>
+        <v>7075626</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5746,7 +5451,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>gammal sälg</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5768,15 +5473,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119142847</v>
+        <v>119142832</v>
       </c>
       <c r="B49" t="n">
-        <v>96860</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5784,21 +5484,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5808,10 +5508,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457373</v>
+        <v>457335</v>
       </c>
       <c r="R49" t="n">
-        <v>7074739</v>
+        <v>7074861</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5854,6 +5554,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>gammal sälg</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5874,15 +5579,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119142900</v>
+        <v>119142854</v>
       </c>
       <c r="B50" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5890,21 +5590,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5914,10 +5614,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457262</v>
+        <v>457372</v>
       </c>
       <c r="R50" t="n">
-        <v>7075622</v>
+        <v>7075470</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5985,15 +5685,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119142842</v>
+        <v>119142870</v>
       </c>
       <c r="B51" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6001,21 +5696,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6025,10 +5720,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457401</v>
+        <v>457301</v>
       </c>
       <c r="R51" t="n">
-        <v>7075404</v>
+        <v>7075616</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6096,37 +5791,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119142822</v>
+        <v>119142873</v>
       </c>
       <c r="B52" t="n">
-        <v>90578</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6136,10 +5826,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457338</v>
+        <v>457187</v>
       </c>
       <c r="R52" t="n">
-        <v>7074790</v>
+        <v>7075735</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6182,6 +5872,11 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6202,15 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119142959</v>
+        <v>119142824</v>
       </c>
       <c r="B53" t="n">
-        <v>79571</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6218,21 +5908,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229748</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457285</v>
+        <v>457186</v>
       </c>
       <c r="R53" t="n">
-        <v>7075614</v>
+        <v>7075734</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6313,37 +6003,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119142935</v>
+        <v>119142842</v>
       </c>
       <c r="B54" t="n">
-        <v>79606</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6353,10 +6038,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457336</v>
+        <v>457401</v>
       </c>
       <c r="R54" t="n">
-        <v>7074860</v>
+        <v>7075404</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6402,7 +6087,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>gammal sälg</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6424,15 +6109,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119142920</v>
+        <v>119142852</v>
       </c>
       <c r="B55" t="n">
-        <v>97804</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6440,21 +6120,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219795</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6464,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457197</v>
+        <v>457238</v>
       </c>
       <c r="R55" t="n">
-        <v>7075738</v>
+        <v>7075699</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6510,6 +6190,11 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6530,37 +6215,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119142780</v>
+        <v>119142868</v>
       </c>
       <c r="B56" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6570,10 +6250,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457219</v>
+        <v>457330</v>
       </c>
       <c r="R56" t="n">
-        <v>7074747</v>
+        <v>7074858</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6616,6 +6296,11 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>gammal sälg</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6636,15 +6321,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119142908</v>
+        <v>119142900</v>
       </c>
       <c r="B57" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,10 +6356,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457251</v>
+        <v>457262</v>
       </c>
       <c r="R57" t="n">
-        <v>7075619</v>
+        <v>7075622</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6747,15 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119142854</v>
+        <v>119142908</v>
       </c>
       <c r="B58" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,21 +6438,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6787,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457372</v>
+        <v>457251</v>
       </c>
       <c r="R58" t="n">
-        <v>7075470</v>
+        <v>7075619</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6858,15 +6533,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119202207</v>
+        <v>119202172</v>
       </c>
       <c r="B59" t="n">
-        <v>94321</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6874,21 +6544,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2813</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6898,10 +6568,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458125</v>
+        <v>458116</v>
       </c>
       <c r="R59" t="n">
-        <v>7074436</v>
+        <v>7074495</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6944,6 +6614,16 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stone/rock on land # block</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6960,50 +6640,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119202142</v>
+        <v>119142859</v>
       </c>
       <c r="B60" t="n">
-        <v>90574</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Höktjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458079</v>
+        <v>457336</v>
       </c>
       <c r="R60" t="n">
-        <v>7074412</v>
+        <v>7074855</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7047,65 +6722,74 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>gammal sälg</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119202240</v>
+        <v>119142791</v>
       </c>
       <c r="B61" t="n">
-        <v>93914</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2359</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Taggstjärnmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Mnium spinosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Voit) Schwägr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Höktjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458100</v>
+        <v>457579</v>
       </c>
       <c r="R61" t="n">
-        <v>7074550</v>
+        <v>7074705</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7152,62 +6836,66 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119202224</v>
+        <v>119142808</v>
       </c>
       <c r="B62" t="n">
-        <v>94309</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Höktjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>458090</v>
+        <v>458008</v>
       </c>
       <c r="R62" t="n">
-        <v>7074520</v>
+        <v>7074657</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7254,62 +6942,66 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119202235</v>
+        <v>119142916</v>
       </c>
       <c r="B63" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Höktjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458114</v>
+        <v>457411</v>
       </c>
       <c r="R63" t="n">
-        <v>7074496</v>
+        <v>7074667</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,40 +7045,29 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stone/rock on land # block</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>119202151</v>
       </c>
       <c r="B64" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7485,50 +7166,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119202122</v>
+        <v>119142861</v>
       </c>
       <c r="B65" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41601</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219847</v>
+        <v>215713</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Höktjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>458100</v>
+        <v>457383</v>
       </c>
       <c r="R65" t="n">
-        <v>7074512</v>
+        <v>7074720</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7575,62 +7251,61 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119202247</v>
+        <v>119142918</v>
       </c>
       <c r="B66" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Höktjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458079</v>
+        <v>457441</v>
       </c>
       <c r="R66" t="n">
-        <v>7074414</v>
+        <v>7075660</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7677,15 +7352,1647 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>119142920</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>457197</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7075738</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>119142856</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>457435</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7075608</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>119142785</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>457489</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7074984</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>119202122</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fjällflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>458100</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7074512</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
           <t>Jesper Wadstein</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
+      <c r="AX70" t="inlineStr">
         <is>
           <t>Jesper Wadstein</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>119142944</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>457328</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7074859</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>119142847</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>457373</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7074739</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>119142877</v>
+      </c>
+      <c r="B73" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>457202</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7075739</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>119142923</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>457271</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7075696</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>119142930</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>457432</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7074665</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>119202235</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fjällflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>458114</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7074496</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Stone/rock on land # block</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>119142860</v>
+      </c>
+      <c r="B77" t="n">
+        <v>81390</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>229558</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Barkporlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pertusaria sommerfeltii</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Flörke ex Sommerf.) Fr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>457287</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7075658</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>119142959</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>457285</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7075614</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>119142760</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6008463</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cheiromycina petri</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D.Hawksw. &amp; Poelt</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>457903</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7074728</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>död ved björk</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>119142893</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6008463</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cheiromycina petri</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D.Hawksw. &amp; Poelt</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>457337</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7074856</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>gammal sälg</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>119142939</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6008463</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cheiromycina petri</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D.Hawksw. &amp; Poelt</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>457279</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7075617</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>119142768</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80341</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6331316</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Rostania effusa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>A.Košuth. et al.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Höktjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>457882</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7074728</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7806-2024 artfynd.xlsx
+++ b/artfynd/A 7806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142903</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142815</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142888</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142863</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142850</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142937</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142752</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202142</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142755</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603636</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142938</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142884</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2107,6 +2177,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142890</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2213,6 +2288,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142909</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142933</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2425,6 +2510,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142935</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142922</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202240</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2724,6 +2824,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142829</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2825,6 +2930,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142786</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142926</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142806</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3124,6 +3244,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202224</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202207</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118804813</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3419,6 +3554,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142774</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3520,6 +3660,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142776</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3621,6 +3766,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142911</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3722,6 +3872,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142948</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3823,6 +3978,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142758</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3920,6 +4080,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202247</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4021,6 +4186,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142771</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4122,6 +4292,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142780</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4223,6 +4398,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142792</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4324,6 +4504,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142817</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4425,6 +4610,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142895</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4526,6 +4716,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142927</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4627,6 +4822,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142942</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4733,6 +4933,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142837</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4839,6 +5044,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142862</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4945,6 +5155,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142902</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5051,6 +5266,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142934</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5157,6 +5377,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142954</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5258,6 +5483,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142950</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5364,6 +5594,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142805</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5470,6 +5705,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142831</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5576,6 +5816,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142832</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5682,6 +5927,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142854</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5788,6 +6038,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142870</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5894,6 +6149,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142873</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6000,6 +6260,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142824</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6106,6 +6371,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142842</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6212,6 +6482,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142852</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6318,6 +6593,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142868</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6424,6 +6704,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142900</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6530,6 +6815,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142908</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6637,6 +6927,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202172</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6743,6 +7038,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142859</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6849,6 +7149,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142791</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6955,6 +7260,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142808</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7061,6 +7371,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142916</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7163,6 +7478,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202151</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7264,6 +7584,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142861</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7365,6 +7690,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142918</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7466,6 +7796,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142920</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7567,6 +7902,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142856</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7668,6 +8008,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142785</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7765,6 +8110,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202122</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7866,6 +8216,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142944</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7967,6 +8322,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142847</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8068,6 +8428,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142877</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8169,6 +8534,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142923</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8270,6 +8640,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142930</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8377,6 +8752,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202235</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8483,6 +8863,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142860</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8589,6 +8974,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142959</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8690,6 +9080,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142760</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8791,6 +9186,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142893</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8892,6 +9292,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142939</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8993,8 +9398,96 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142768</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>